--- a/data/WP18/WP18_beteiligte_ministerien.xlsx
+++ b/data/WP18/WP18_beteiligte_ministerien.xlsx
@@ -377,17 +377,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3636</v>
+        <v>3637</v>
       </c>
       <c r="C2" t="n">
         <v>35.3454345434542</v>
       </c>
-      <c r="D2" t="n">
-        <v>2578</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.0979097909791</v>
-      </c>
+      <c r="D2"/>
+      <c r="E2"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -708,13 +704,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5375993-4D45-4FCA-BC8E-F1EDD3BC376F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E52DFA09-AB4B-4ADE-B76E-1F6FB46BACBD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7FF16CD-B9DC-4BAF-AD2C-8520D7068BBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F598F915-EEC2-4763-BE76-80279A3A3591}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8342D61-D03E-433C-9388-D926F683FCB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62BDE62A-E71C-4B18-B3B4-3188878383F8}"/>
 </file>
--- a/data/WP18/WP18_beteiligte_ministerien.xlsx
+++ b/data/WP18/WP18_beteiligte_ministerien.xlsx
@@ -377,29 +377,33 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="C2" t="n">
-        <v>35.3454345434542</v>
-      </c>
-      <c r="D2"/>
-      <c r="E2"/>
+        <v>34.796204620462</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2475</v>
+      </c>
+      <c r="E2" t="n">
+        <v>31.9306930693069</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="C3" t="n">
-        <v>35.67283189478</v>
+        <v>35.2169268693508</v>
       </c>
       <c r="D3" t="n">
-        <v>1877</v>
+        <v>1805</v>
       </c>
       <c r="E3" t="n">
-        <v>22.852445540485</v>
+        <v>25.8422350041085</v>
       </c>
     </row>
     <row r="4">
@@ -410,13 +414,13 @@
         <v>942</v>
       </c>
       <c r="C4" t="n">
-        <v>38.2441613588111</v>
+        <v>37.8407643312102</v>
       </c>
       <c r="D4" t="n">
-        <v>804</v>
+        <v>787</v>
       </c>
       <c r="E4" t="n">
-        <v>14.6496815286624</v>
+        <v>16.4543524416136</v>
       </c>
     </row>
     <row r="5">
@@ -427,13 +431,13 @@
         <v>277</v>
       </c>
       <c r="C5" t="n">
-        <v>37.8447653429603</v>
+        <v>37.5812274368231</v>
       </c>
       <c r="D5" t="n">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="E5" t="n">
-        <v>11.5523465703971</v>
+        <v>14.0794223826715</v>
       </c>
     </row>
     <row r="6">
@@ -444,13 +448,13 @@
         <v>46</v>
       </c>
       <c r="C6" t="n">
-        <v>37.0869565217391</v>
+        <v>36.6739130434783</v>
       </c>
       <c r="D6" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" t="n">
-        <v>10.8695652173913</v>
+        <v>15.2173913043478</v>
       </c>
     </row>
     <row r="7">
@@ -461,7 +465,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>35.5714285714286</v>
+        <v>35.4285714285714</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -704,13 +708,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E52DFA09-AB4B-4ADE-B76E-1F6FB46BACBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8907B83A-4753-479E-B921-59F101707854}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F598F915-EEC2-4763-BE76-80279A3A3591}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA18E70A-E425-4979-9F15-02CAF4E16605}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62BDE62A-E71C-4B18-B3B4-3188878383F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF7525E9-D5F8-4B44-AC46-8D97054CE4D5}"/>
 </file>
--- a/data/WP18/WP18_beteiligte_ministerien.xlsx
+++ b/data/WP18/WP18_beteiligte_ministerien.xlsx
@@ -383,10 +383,10 @@
         <v>34.796204620462</v>
       </c>
       <c r="D2" t="n">
-        <v>2475</v>
+        <v>2703</v>
       </c>
       <c r="E2" t="n">
-        <v>31.9306930693069</v>
+        <v>25.6600660066007</v>
       </c>
     </row>
     <row r="3">
@@ -400,10 +400,10 @@
         <v>35.2169268693508</v>
       </c>
       <c r="D3" t="n">
-        <v>1805</v>
+        <v>1969</v>
       </c>
       <c r="E3" t="n">
-        <v>25.8422350041085</v>
+        <v>19.1043549712408</v>
       </c>
     </row>
     <row r="4">
@@ -417,10 +417,10 @@
         <v>37.8407643312102</v>
       </c>
       <c r="D4" t="n">
-        <v>787</v>
+        <v>826</v>
       </c>
       <c r="E4" t="n">
-        <v>16.4543524416136</v>
+        <v>12.3142250530786</v>
       </c>
     </row>
     <row r="5">
@@ -434,10 +434,10 @@
         <v>37.5812274368231</v>
       </c>
       <c r="D5" t="n">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="E5" t="n">
-        <v>14.0794223826715</v>
+        <v>8.66425992779783</v>
       </c>
     </row>
     <row r="6">
@@ -708,13 +708,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8907B83A-4753-479E-B921-59F101707854}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{895E9C6B-C064-4F65-8E97-9765359A6187}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA18E70A-E425-4979-9F15-02CAF4E16605}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098D85CE-6529-4395-9E5E-A20326EE7D4C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF7525E9-D5F8-4B44-AC46-8D97054CE4D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC087100-0F98-4DA4-9912-81590D7BDE38}"/>
 </file>